--- a/07. MS Excel - zadania maturalne/zadanie11.xlsx
+++ b/07. MS Excel - zadania maturalne/zadanie11.xlsx
@@ -371,11 +371,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="-1305698352"/>
-        <c:axId val="-806794944"/>
+        <c:axId val="1621319696"/>
+        <c:axId val="1621321872"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="-1305698352"/>
+        <c:axId val="1621319696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -474,7 +474,7 @@
             <a:endParaRPr lang="pl-PL"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-806794944"/>
+        <c:crossAx val="1621321872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -482,7 +482,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-806794944"/>
+        <c:axId val="1621321872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -589,7 +589,7 @@
             <a:endParaRPr lang="pl-PL"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-1305698352"/>
+        <c:crossAx val="1621319696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4922,7 +4922,7 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <f t="shared" ref="H3:H13" si="3">AVERAGEIF($E$2:$E$205,G4,$D$2:$D$205)</f>
+        <f t="shared" ref="H4:H13" si="3">AVERAGEIF($E$2:$E$205,G4,$D$2:$D$205)</f>
         <v>219.23529411764707</v>
       </c>
     </row>
